--- a/Manual_Testing/Day2/Shaadi_application/TestDeliverables B VISHNUVARDAN(85010893).xlsx
+++ b/Manual_Testing/Day2/Shaadi_application/TestDeliverables B VISHNUVARDAN(85010893).xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishnu Vardan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f43bb820658f1ef9/Desktop/BootCamp_Testing/Manual_Testing/Day2/Shaadi_application/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394C4D5D-A8C3-4A67-97ED-FF5C1803BE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
